--- a/entrepreneur_forms/026_square_meal_kit_delivery_subscription_form--entrepreneur_forms.xlsx
+++ b/entrepreneur_forms/026_square_meal_kit_delivery_subscription_form--entrepreneur_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'premium'}</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Premium'}</t>
+          <t>Premium</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'business'}</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Business'}</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'breakfast'}</t>
+          <t>breakfast</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Breakfast'}</t>
+          <t>Breakfast</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'lunch'}</t>
+          <t>lunch</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Lunch'}</t>
+          <t>Lunch</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'dinner'}</t>
+          <t>dinner</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Dinner'}</t>
+          <t>Dinner</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'cvv'}</t>
+          <t>cvv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'CVV'}</t>
+          <t>CVV</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'security_code'}</t>
+          <t>security_code</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Security Code'}</t>
+          <t>Security Code</t>
         </is>
       </c>
     </row>
